--- a/scripts/EU_Figures/2025Q4_EU_Figures.xlsx
+++ b/scripts/EU_Figures/2025Q4_EU_Figures.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Euro Area Figures" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EU Productivity Figures" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjusted Eurozone GVAH" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unadjusted Eurozone GVAH" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjusted Eurozone GVA per hour" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unadjusted Eurozone GVA per hour" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2835197.45</v>
+        <v>2835194.5</v>
       </c>
       <c r="C2" t="n">
         <v>65709428</v>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2837563.4</v>
+        <v>2837565.36</v>
       </c>
       <c r="C3" t="n">
         <v>65729377</v>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2843341.31</v>
+        <v>2843343.26</v>
       </c>
       <c r="C4" t="n">
         <v>66026966</v>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2860133.55</v>
+        <v>2860130.59</v>
       </c>
       <c r="C5" t="n">
         <v>66070125</v>
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2861700.59</v>
+        <v>2861692.71</v>
       </c>
       <c r="C6" t="n">
         <v>66354796</v>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2869551.73</v>
+        <v>2869555.31</v>
       </c>
       <c r="C7" t="n">
         <v>66445746</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2873979.6</v>
+        <v>2873989.72</v>
       </c>
       <c r="C8" t="n">
         <v>66405191</v>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2876843.71</v>
+        <v>2876839.09</v>
       </c>
       <c r="C9" t="n">
         <v>66755243</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2887655.39</v>
+        <v>2887639.31</v>
       </c>
       <c r="C10" t="n">
         <v>66707656</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2893118.9</v>
+        <v>2893123.3</v>
       </c>
       <c r="C11" t="n">
         <v>66648222</v>
@@ -2400,7 +2400,7 @@
         <v>0.28</v>
       </c>
       <c r="F11" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="12">
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2902323.15</v>
+        <v>2902342.28</v>
       </c>
       <c r="C12" t="n">
         <v>66857011</v>
@@ -2419,7 +2419,7 @@
         <v>43.41</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F12" t="n">
         <v>0.3</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2912662.79</v>
+        <v>2912653.26</v>
       </c>
       <c r="C13" t="n">
         <v>67234318</v>

--- a/scripts/EU_Figures/2025Q4_EU_Figures.xlsx
+++ b/scripts/EU_Figures/2025Q4_EU_Figures.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>1.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="3">
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="4">
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="F4" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="5">
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.39</v>
+        <v>-0.35</v>
       </c>
       <c r="E5" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="F5" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="6">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="E6" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="F6" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="7">
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0.84</v>
       </c>
       <c r="F7" t="n">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="8">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="F8" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="9">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="F9" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -692,7 +692,7 @@
         <v>0.18</v>
       </c>
       <c r="E10" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>5.16</v>
@@ -718,7 +718,7 @@
         <v>0.18</v>
       </c>
       <c r="E11" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F11" t="n">
         <v>5.35</v>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="E13" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="F13" t="n">
-        <v>5.73</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="14">
@@ -793,13 +793,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="E14" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="F14" t="n">
-        <v>6.67</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="15">
@@ -822,10 +822,10 @@
         <v>0.14</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="F15" t="n">
-        <v>6.82</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="16">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="F16" t="n">
-        <v>7.17</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="E17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="F17" t="n">
-        <v>7.37</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="18">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="F18" t="n">
-        <v>4.35</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="19">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="E19" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="F19" t="n">
         <v>4.35</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="E20" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="F20" t="n">
-        <v>4.73</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="21">
@@ -978,10 +978,10 @@
         <v>0.54</v>
       </c>
       <c r="E21" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="F21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.39</v>
+        <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="F2" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="3">
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="F3" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="4">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="E4" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="F4" t="n">
-        <v>5.73</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="5">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="F5" t="n">
-        <v>7.37</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="6">
@@ -1154,10 +1154,10 @@
         <v>0.54</v>
       </c>
       <c r="E6" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="7">
@@ -1180,10 +1180,10 @@
         <v>-0.28</v>
       </c>
       <c r="E7" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="8">
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="F8" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="F10" t="n">
-        <v>7.95</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="E11" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="F11" t="n">
-        <v>4.66</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="12">
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.29</v>
+        <v>1.1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="F23" t="n">
-        <v>18.76</v>
+        <v>19.19</v>
       </c>
     </row>
     <row r="24">
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="E24" t="n">
-        <v>6.65</v>
+        <v>6.62</v>
       </c>
       <c r="F24" t="n">
-        <v>49.42</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="25">
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="E25" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="26">
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2835194.5</v>
+        <v>2835199.21</v>
       </c>
       <c r="C2" t="n">
-        <v>65709428</v>
+        <v>65711357</v>
       </c>
       <c r="D2" t="n">
         <v>43.15</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2837565.36</v>
+        <v>2837555.74</v>
       </c>
       <c r="C3" t="n">
-        <v>65729377</v>
+        <v>65730690</v>
       </c>
       <c r="D3" t="n">
         <v>43.17</v>
@@ -2239,16 +2239,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2843343.26</v>
+        <v>2843329.58</v>
       </c>
       <c r="C4" t="n">
-        <v>66026966</v>
+        <v>66025867</v>
       </c>
       <c r="D4" t="n">
         <v>43.06</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2860130.59</v>
+        <v>2860078.97</v>
       </c>
       <c r="C5" t="n">
-        <v>66070125</v>
+        <v>66067101</v>
       </c>
       <c r="D5" t="n">
         <v>43.29</v>
       </c>
       <c r="E5" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -2279,16 +2279,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2861692.71</v>
+        <v>2861684.44</v>
       </c>
       <c r="C6" t="n">
-        <v>66354796</v>
+        <v>66359042</v>
       </c>
       <c r="D6" t="n">
-        <v>43.13</v>
+        <v>43.12</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.37</v>
+        <v>-0.38</v>
       </c>
       <c r="F6" t="n">
         <v>-0.05</v>
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2869555.31</v>
+        <v>2869534.11</v>
       </c>
       <c r="C7" t="n">
-        <v>66445746</v>
+        <v>66447496</v>
       </c>
       <c r="D7" t="n">
-        <v>43.19</v>
+        <v>43.18</v>
       </c>
       <c r="E7" t="n">
         <v>0.14</v>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2873989.72</v>
+        <v>2873960.97</v>
       </c>
       <c r="C8" t="n">
-        <v>66405191</v>
+        <v>66402926</v>
       </c>
       <c r="D8" t="n">
         <v>43.28</v>
@@ -2345,19 +2345,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2876839.09</v>
+        <v>2876820.89</v>
       </c>
       <c r="C9" t="n">
-        <v>66755243</v>
+        <v>66749930</v>
       </c>
       <c r="D9" t="n">
         <v>43.1</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="10">
@@ -2367,16 +2367,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2887639.31</v>
+        <v>2887668.26</v>
       </c>
       <c r="C10" t="n">
-        <v>66707656</v>
+        <v>66714989</v>
       </c>
       <c r="D10" t="n">
-        <v>43.29</v>
+        <v>43.28</v>
       </c>
       <c r="E10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="F10" t="n">
         <v>0.37</v>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2893123.3</v>
+        <v>2893118.46</v>
       </c>
       <c r="C11" t="n">
-        <v>66648222</v>
+        <v>66650139</v>
       </c>
       <c r="D11" t="n">
         <v>43.41</v>
       </c>
       <c r="E11" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="F11" t="n">
         <v>0.52</v>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2902342.28</v>
+        <v>2902314.59</v>
       </c>
       <c r="C12" t="n">
-        <v>66857011</v>
+        <v>66853376</v>
       </c>
       <c r="D12" t="n">
         <v>43.41</v>
@@ -2423,7 +2423,7 @@
         <v>0.01</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="13">
@@ -2433,19 +2433,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2912653.26</v>
+        <v>2912575.44</v>
       </c>
       <c r="C13" t="n">
-        <v>67234318</v>
+        <v>67226154</v>
       </c>
       <c r="D13" t="n">
-        <v>43.32</v>
+        <v>43.33</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2894152.51</v>
+        <v>2894061.87</v>
       </c>
       <c r="C2" t="n">
-        <v>65709428</v>
+        <v>65711357</v>
       </c>
       <c r="D2" t="n">
         <v>44.04</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2897620.92</v>
+        <v>2897489.29</v>
       </c>
       <c r="C3" t="n">
-        <v>65729377</v>
+        <v>65730690</v>
       </c>
       <c r="D3" t="n">
         <v>44.08</v>
@@ -2539,16 +2539,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2899231.45</v>
+        <v>2899112.49</v>
       </c>
       <c r="C4" t="n">
-        <v>66026966</v>
+        <v>66025867</v>
       </c>
       <c r="D4" t="n">
         <v>43.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2915086.53</v>
+        <v>2914839</v>
       </c>
       <c r="C5" t="n">
-        <v>66070125</v>
+        <v>66067101</v>
       </c>
       <c r="D5" t="n">
         <v>44.12</v>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2914428.1</v>
+        <v>2914545.55</v>
       </c>
       <c r="C6" t="n">
-        <v>66354796</v>
+        <v>66359042</v>
       </c>
       <c r="D6" t="n">
         <v>43.92</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2924028.26</v>
+        <v>2924049.69</v>
       </c>
       <c r="C7" t="n">
-        <v>66445746</v>
+        <v>66447496</v>
       </c>
       <c r="D7" t="n">
         <v>44.01</v>
@@ -2613,7 +2613,7 @@
         <v>0.19</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="8">
@@ -2623,19 +2623,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2935154.85</v>
+        <v>2935177</v>
       </c>
       <c r="C8" t="n">
-        <v>66405191</v>
+        <v>66402926</v>
       </c>
       <c r="D8" t="n">
         <v>44.2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="F8" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="9">
@@ -2645,19 +2645,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2940893.47</v>
+        <v>2940754.58</v>
       </c>
       <c r="C9" t="n">
-        <v>66755243</v>
+        <v>66749930</v>
       </c>
       <c r="D9" t="n">
-        <v>44.05</v>
+        <v>44.06</v>
       </c>
       <c r="E9" t="n">
         <v>-0.33</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="10">
@@ -2667,16 +2667,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2958948.89</v>
+        <v>2959162.66</v>
       </c>
       <c r="C10" t="n">
-        <v>66707656</v>
+        <v>66714989</v>
       </c>
       <c r="D10" t="n">
         <v>44.36</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="F10" t="n">
         <v>0.99</v>
@@ -2689,16 +2689,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2965328.22</v>
+        <v>2965360.49</v>
       </c>
       <c r="C11" t="n">
-        <v>66648222</v>
+        <v>66650139</v>
       </c>
       <c r="D11" t="n">
         <v>44.49</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="F11" t="n">
         <v>1.1</v>
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2974432.33</v>
+        <v>2974472.16</v>
       </c>
       <c r="C12" t="n">
-        <v>66857011</v>
+        <v>66853376</v>
       </c>
       <c r="D12" t="n">
         <v>44.49</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="13">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2984159.05</v>
+        <v>2983913.56</v>
       </c>
       <c r="C13" t="n">
-        <v>67234318</v>
+        <v>67226154</v>
       </c>
       <c r="D13" t="n">
-        <v>44.38</v>
+        <v>44.39</v>
       </c>
       <c r="E13" t="n">
         <v>-0.24</v>
@@ -5310,7 +5310,7 @@
         <v>43.91</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="E124" t="inlineStr"/>
     </row>
@@ -5372,7 +5372,7 @@
         <v>0.19</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="128">
@@ -5390,10 +5390,10 @@
         <v>44.2</v>
       </c>
       <c r="D128" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="E128" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="129">
@@ -5408,13 +5408,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>44.05</v>
+        <v>44.06</v>
       </c>
       <c r="D129" t="n">
         <v>-0.33</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="130">
@@ -5432,7 +5432,7 @@
         <v>44.36</v>
       </c>
       <c r="D130" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="E130" t="n">
         <v>0.99</v>
@@ -5453,7 +5453,7 @@
         <v>44.49</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="E131" t="n">
         <v>1.1</v>
@@ -5474,10 +5474,10 @@
         <v>44.49</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="133">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>44.38</v>
+        <v>44.39</v>
       </c>
       <c r="D133" t="n">
         <v>-0.24</v>
@@ -5552,7 +5552,7 @@
         <v>43.06</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="E136" t="inlineStr"/>
     </row>
@@ -5571,7 +5571,7 @@
         <v>43.29</v>
       </c>
       <c r="D137" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="E137" t="inlineStr"/>
     </row>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>43.13</v>
+        <v>43.12</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.37</v>
+        <v>-0.38</v>
       </c>
       <c r="E138" t="n">
         <v>-0.05</v>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>43.19</v>
+        <v>43.18</v>
       </c>
       <c r="D139" t="n">
         <v>0.14</v>
@@ -5653,10 +5653,10 @@
         <v>43.1</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="142">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>43.29</v>
+        <v>43.28</v>
       </c>
       <c r="D142" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="E142" t="n">
         <v>0.37</v>
@@ -5695,7 +5695,7 @@
         <v>43.41</v>
       </c>
       <c r="D143" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="E143" t="n">
         <v>0.52</v>
@@ -5719,7 +5719,7 @@
         <v>0.01</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="145">
@@ -5734,13 +5734,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>43.32</v>
+        <v>43.33</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="E145" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="146">
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>16.5</v>
+        <v>16.49</v>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>16.5</v>
+        <v>16.49</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -7276,7 +7276,7 @@
         <v>16.64</v>
       </c>
       <c r="D220" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="E220" t="inlineStr"/>
     </row>
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>16.83</v>
+        <v>16.84</v>
       </c>
       <c r="D222" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="E222" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="223">
@@ -7332,13 +7332,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>16.83</v>
+        <v>16.84</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
       </c>
       <c r="E223" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="224">
@@ -7356,10 +7356,10 @@
         <v>16.64</v>
       </c>
       <c r="D224" t="n">
-        <v>-1.17</v>
+        <v>-1.14</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="225">
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="226">
@@ -7395,13 +7395,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>16.37</v>
+        <v>16.36</v>
       </c>
       <c r="D226" t="n">
-        <v>-1.58</v>
+        <v>-1.69</v>
       </c>
       <c r="E226" t="n">
-        <v>-2.73</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="227">
@@ -7416,13 +7416,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>16.37</v>
+        <v>16.36</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
       </c>
       <c r="E227" t="n">
-        <v>-2.73</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="228">
@@ -7437,13 +7437,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>16.76</v>
+        <v>16.75</v>
       </c>
       <c r="D228" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="E228" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="229">
@@ -7458,13 +7458,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>16.76</v>
+        <v>16.75</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
       </c>
       <c r="E229" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="230">
@@ -7482,10 +7482,10 @@
         <v>16.9</v>
       </c>
       <c r="D230" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="E230" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="231">
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="E231" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="232">
@@ -7521,13 +7521,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>16.84</v>
+        <v>16.85</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
       <c r="E232" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="233">
@@ -7542,13 +7542,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>16.84</v>
+        <v>16.85</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="234">
@@ -7563,13 +7563,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>17.08</v>
+        <v>17.06</v>
       </c>
       <c r="D234" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="E234" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="235">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>17.08</v>
+        <v>17.06</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
       </c>
       <c r="E235" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="236">
@@ -7605,13 +7605,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>16.92</v>
+        <v>16.91</v>
       </c>
       <c r="D236" t="n">
-        <v>-0.92</v>
+        <v>-0.84</v>
       </c>
       <c r="E236" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="237">
@@ -7626,13 +7626,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>16.92</v>
+        <v>16.91</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
       </c>
       <c r="E237" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="238">
@@ -7647,13 +7647,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>17.27</v>
+        <v>17.28</v>
       </c>
       <c r="D238" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="E238" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="239">
@@ -7668,13 +7668,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>17.27</v>
+        <v>17.28</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
       </c>
       <c r="E239" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="240">
@@ -7689,13 +7689,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>16.89</v>
+        <v>16.91</v>
       </c>
       <c r="D240" t="n">
-        <v>-2.18</v>
+        <v>-2.11</v>
       </c>
       <c r="E240" t="n">
-        <v>-0.15</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="241">
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>16.89</v>
+        <v>16.91</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
       </c>
       <c r="E241" t="n">
-        <v>-0.15</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="242">
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>99.34999999999999</v>
+        <v>99.22</v>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>102.85</v>
+        <v>102.67</v>
       </c>
       <c r="D243" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="E243" t="inlineStr"/>
     </row>
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>98.78</v>
+        <v>98.75</v>
       </c>
       <c r="D244" t="n">
-        <v>-3.95</v>
+        <v>-3.82</v>
       </c>
       <c r="E244" t="inlineStr"/>
     </row>
@@ -7786,10 +7786,10 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>99.45</v>
+        <v>99.39</v>
       </c>
       <c r="D245" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="E245" t="inlineStr"/>
     </row>
@@ -7805,13 +7805,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>95.22</v>
+        <v>95.2</v>
       </c>
       <c r="D246" t="n">
-        <v>-4.25</v>
+        <v>-4.22</v>
       </c>
       <c r="E246" t="n">
-        <v>-4.15</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="247">
@@ -7826,13 +7826,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>97.45</v>
+        <v>97.41</v>
       </c>
       <c r="D247" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="E247" t="n">
-        <v>-5.25</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="248">
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>102.93</v>
+        <v>103.1</v>
       </c>
       <c r="D248" t="n">
-        <v>5.63</v>
+        <v>5.84</v>
       </c>
       <c r="E248" t="n">
-        <v>4.2</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="249">
@@ -7868,13 +7868,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>105.54</v>
+        <v>105.62</v>
       </c>
       <c r="D249" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="E249" t="n">
-        <v>6.12</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="250">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>111.91</v>
+        <v>111.78</v>
       </c>
       <c r="D250" t="n">
-        <v>6.04</v>
+        <v>5.83</v>
       </c>
       <c r="E250" t="n">
-        <v>17.52</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="251">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>111.38</v>
+        <v>111.34</v>
       </c>
       <c r="D251" t="n">
-        <v>-0.47</v>
+        <v>-0.39</v>
       </c>
       <c r="E251" t="n">
         <v>14.3</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>111.08</v>
+        <v>111.32</v>
       </c>
       <c r="D252" t="n">
-        <v>-0.27</v>
+        <v>-0.02</v>
       </c>
       <c r="E252" t="n">
-        <v>7.92</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="253">
@@ -7952,13 +7952,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>109.66</v>
+        <v>109.81</v>
       </c>
       <c r="D253" t="n">
-        <v>-1.28</v>
+        <v>-1.35</v>
       </c>
       <c r="E253" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="254">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>48.57</v>
+        <v>48.53</v>
       </c>
       <c r="D255" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="E255" t="inlineStr"/>
     </row>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>48.46</v>
+        <v>48.48</v>
       </c>
       <c r="D256" t="n">
-        <v>-0.23</v>
+        <v>-0.1</v>
       </c>
       <c r="E256" t="inlineStr"/>
     </row>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>49.44</v>
+        <v>49.5</v>
       </c>
       <c r="D257" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="E257" t="inlineStr"/>
     </row>
@@ -8047,13 +8047,13 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>48.55</v>
+        <v>48.48</v>
       </c>
       <c r="D258" t="n">
-        <v>-1.8</v>
+        <v>-2.05</v>
       </c>
       <c r="E258" t="n">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="259">
@@ -8068,13 +8068,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>48.96</v>
+        <v>48.92</v>
       </c>
       <c r="D259" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="E259" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="260">
@@ -8089,13 +8089,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>49.29</v>
+        <v>49.35</v>
       </c>
       <c r="D260" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="E260" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="261">
@@ -8110,13 +8110,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>49.25</v>
+        <v>49.34</v>
       </c>
       <c r="D261" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E261" t="n">
-        <v>-0.38</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="262">
@@ -8131,13 +8131,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>49.24</v>
+        <v>49.12</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.02</v>
+        <v>-0.46</v>
       </c>
       <c r="E262" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="263">
@@ -8152,13 +8152,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>48.56</v>
+        <v>48.53</v>
       </c>
       <c r="D263" t="n">
-        <v>-1.38</v>
+        <v>-1.19</v>
       </c>
       <c r="E263" t="n">
-        <v>-0.82</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="264">
@@ -8173,13 +8173,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>48.44</v>
+        <v>48.52</v>
       </c>
       <c r="D264" t="n">
-        <v>-0.25</v>
+        <v>-0.03</v>
       </c>
       <c r="E264" t="n">
-        <v>-1.73</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="265">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>48.44</v>
+        <v>48.57</v>
       </c>
       <c r="D265" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="E265" t="n">
-        <v>-1.64</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="266">
@@ -9697,7 +9697,7 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>81.56999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>81.56999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D339" t="n">
         <v>0</v>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>82.5</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D340" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="E340" t="inlineStr"/>
     </row>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>82.5</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D341" t="n">
         <v>0</v>
@@ -9771,13 +9771,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>82.52</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D342" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E342" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="343">
@@ -9792,13 +9792,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>82.52</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D343" t="n">
         <v>0</v>
       </c>
       <c r="E343" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="344">
@@ -9813,13 +9813,13 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>81.51000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="D344" t="n">
-        <v>-1.22</v>
+        <v>-1.38</v>
       </c>
       <c r="E344" t="n">
-        <v>-1.2</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="345">
@@ -9834,13 +9834,13 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>81.51000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="D345" t="n">
         <v>0</v>
       </c>
       <c r="E345" t="n">
-        <v>-1.2</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="346">
@@ -9855,13 +9855,13 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>83.70999999999999</v>
+        <v>83.62</v>
       </c>
       <c r="D346" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="E346" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="347">
@@ -9876,13 +9876,13 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>83.70999999999999</v>
+        <v>83.62</v>
       </c>
       <c r="D347" t="n">
         <v>0</v>
       </c>
       <c r="E347" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="348">
@@ -9897,13 +9897,13 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>83.68000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="D348" t="n">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="E348" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="349">
@@ -9918,13 +9918,13 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>83.68000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="D349" t="n">
         <v>0</v>
       </c>
       <c r="E349" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="350">
@@ -9939,13 +9939,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>80.43000000000001</v>
+        <v>80.27</v>
       </c>
       <c r="D350" t="n">
-        <v>-3.88</v>
+        <v>-3.9</v>
       </c>
       <c r="E350" t="n">
-        <v>-3.91</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="351">
@@ -9960,13 +9960,13 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>80.43000000000001</v>
+        <v>80.27</v>
       </c>
       <c r="D351" t="n">
         <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>-3.91</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="352">
@@ -9981,13 +9981,13 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>80.08</v>
+        <v>80.12</v>
       </c>
       <c r="D352" t="n">
-        <v>-0.44</v>
+        <v>-0.18</v>
       </c>
       <c r="E352" t="n">
-        <v>-4.3</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="353">
@@ -10002,13 +10002,13 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>80.08</v>
+        <v>80.12</v>
       </c>
       <c r="D353" t="n">
         <v>0</v>
       </c>
       <c r="E353" t="n">
-        <v>-4.3</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="354">
@@ -10023,13 +10023,13 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>80.92</v>
+        <v>81</v>
       </c>
       <c r="D354" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="E354" t="n">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="355">
@@ -10044,13 +10044,13 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>80.92</v>
+        <v>81</v>
       </c>
       <c r="D355" t="n">
         <v>0</v>
       </c>
       <c r="E355" t="n">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="356">
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>80.81999999999999</v>
+        <v>80.83</v>
       </c>
       <c r="D356" t="n">
-        <v>-0.13</v>
+        <v>-0.22</v>
       </c>
       <c r="E356" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="357">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>80.81999999999999</v>
+        <v>80.83</v>
       </c>
       <c r="D357" t="n">
         <v>0</v>
       </c>
       <c r="E357" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="358">
@@ -10107,13 +10107,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>81.73999999999999</v>
+        <v>81.64</v>
       </c>
       <c r="D358" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="E358" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="359">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>81.73999999999999</v>
+        <v>81.64</v>
       </c>
       <c r="D359" t="n">
         <v>0</v>
       </c>
       <c r="E359" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="360">
@@ -10149,13 +10149,13 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>81.48999999999999</v>
+        <v>81.19</v>
       </c>
       <c r="D360" t="n">
-        <v>-0.31</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E360" t="n">
-        <v>0.83</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="361">
@@ -10170,13 +10170,13 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>81.48999999999999</v>
+        <v>81.19</v>
       </c>
       <c r="D361" t="n">
         <v>0</v>
       </c>
       <c r="E361" t="n">
-        <v>0.83</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="362">
@@ -11712,7 +11712,7 @@
         <v>23.34</v>
       </c>
       <c r="D436" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="E436" t="inlineStr"/>
     </row>
@@ -11750,10 +11750,10 @@
         <v>23.57</v>
       </c>
       <c r="D438" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="E438" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="439">
@@ -11774,7 +11774,7 @@
         <v>0</v>
       </c>
       <c r="E439" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="440">
@@ -11795,7 +11795,7 @@
         <v>0.92</v>
       </c>
       <c r="E440" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="441">
@@ -11816,7 +11816,7 @@
         <v>0</v>
       </c>
       <c r="E441" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="442">
@@ -11834,10 +11834,10 @@
         <v>23.61</v>
       </c>
       <c r="D442" t="n">
-        <v>-0.75</v>
+        <v>-0.78</v>
       </c>
       <c r="E442" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="443">
@@ -11858,7 +11858,7 @@
         <v>0</v>
       </c>
       <c r="E443" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="444">
@@ -11876,10 +11876,10 @@
         <v>23.89</v>
       </c>
       <c r="D444" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="E444" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="445">
@@ -11900,7 +11900,7 @@
         <v>0</v>
       </c>
       <c r="E445" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="446">
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>23.76</v>
+        <v>23.77</v>
       </c>
       <c r="D446" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="E446" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="447">
@@ -11936,13 +11936,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>23.76</v>
+        <v>23.77</v>
       </c>
       <c r="D447" t="n">
         <v>0</v>
       </c>
       <c r="E447" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="448">
@@ -11957,13 +11957,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>23.75</v>
+        <v>23.76</v>
       </c>
       <c r="D448" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="E448" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="449">
@@ -11978,13 +11978,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>23.75</v>
+        <v>23.76</v>
       </c>
       <c r="D449" t="n">
         <v>0</v>
       </c>
       <c r="E449" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="450">
@@ -11999,13 +11999,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>24.02</v>
+        <v>24.01</v>
       </c>
       <c r="D450" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="E450" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="451">
@@ -12020,13 +12020,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>24.02</v>
+        <v>24.01</v>
       </c>
       <c r="D451" t="n">
         <v>0</v>
       </c>
       <c r="E451" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="452">
@@ -12041,13 +12041,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>24.03</v>
+        <v>24.02</v>
       </c>
       <c r="D452" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E452" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="453">
@@ -12062,13 +12062,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>24.03</v>
+        <v>24.02</v>
       </c>
       <c r="D453" t="n">
         <v>0</v>
       </c>
       <c r="E453" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="454">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>23.97</v>
+        <v>23.98</v>
       </c>
       <c r="D454" t="n">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="E454" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="455">
@@ -12104,13 +12104,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>23.97</v>
+        <v>23.98</v>
       </c>
       <c r="D455" t="n">
         <v>0</v>
       </c>
       <c r="E455" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="456">
@@ -12125,13 +12125,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>23.91</v>
+        <v>23.92</v>
       </c>
       <c r="D456" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="E456" t="n">
-        <v>-0.5</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="457">
@@ -12146,13 +12146,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>23.91</v>
+        <v>23.92</v>
       </c>
       <c r="D457" t="n">
         <v>0</v>
       </c>
       <c r="E457" t="n">
-        <v>-0.5</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="458">
